--- a/data/exports/黄老师/dist_order_2026-09-22.xlsx
+++ b/data/exports/黄老师/dist_order_2026-09-22.xlsx
@@ -16769,7 +16769,7 @@
       </c>
       <c r="B279" s="0" t="inlineStr">
         <is>
-          <t>小米. ᩚ</t>
+          <t>小澜. ᩚ</t>
         </is>
       </c>
       <c r="C279" s="0" t="inlineStr">
